--- a/Assets/Game/luban/config/tables.xlsx
+++ b/Assets/Game/luban/config/tables.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="13770" windowHeight="6375"/>
+    <workbookView windowWidth="14250" windowHeight="7545"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1139,7 +1139,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="33.8571428571429" style="2" customWidth="1"/>
+    <col min="2" max="2" width="42.7142857142857" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.7142857142857" style="2" customWidth="1"/>
     <col min="4" max="4" width="61.8571428571429" style="2" customWidth="1"/>
     <col min="5" max="5" width="54.4285714285714" style="2" customWidth="1"/>
@@ -1260,8 +1260,8 @@
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="2" t="str">
-        <f>C5&amp;"_container"</f>
-        <v>surname_config_container</v>
+        <f>"container."&amp;L5</f>
+        <v>container.surname_config_container</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>29</v>
@@ -1273,14 +1273,14 @@
         <v>30</v>
       </c>
       <c r="L5" s="2" t="str">
-        <f>B5</f>
+        <f>C5&amp;"_container"</f>
         <v>surname_config_container</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="2" t="str">
-        <f>C6&amp;"_container"</f>
-        <v>name_config_container</v>
+        <f>"container."&amp;L6</f>
+        <v>container.name_config_container</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>31</v>
@@ -1292,14 +1292,14 @@
         <v>32</v>
       </c>
       <c r="L6" s="2" t="str">
-        <f>B6</f>
+        <f>C6&amp;"_container"</f>
         <v>name_config_container</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="2" t="str">
-        <f>C7&amp;"_container"</f>
-        <v>red_dot_config_container</v>
+        <f>"container."&amp;L7</f>
+        <v>container.red_dot_config_container</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>33</v>
@@ -1311,14 +1311,14 @@
         <v>34</v>
       </c>
       <c r="L7" s="2" t="str">
-        <f>B7</f>
+        <f>C7&amp;"_container"</f>
         <v>red_dot_config_container</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="2" t="str">
-        <f>C8&amp;"_container"</f>
-        <v>item_config_container</v>
+        <f>"container."&amp;L8</f>
+        <v>container.item_config_container</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>35</v>
@@ -1330,14 +1330,14 @@
         <v>36</v>
       </c>
       <c r="L8" s="2" t="str">
-        <f>B8</f>
+        <f>C8&amp;"_container"</f>
         <v>item_config_container</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="2" t="str">
-        <f>C9&amp;"_container"</f>
-        <v>develop_config_container</v>
+        <f>"container."&amp;L9</f>
+        <v>container.develop_config_container</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>37</v>
@@ -1349,7 +1349,7 @@
         <v>38</v>
       </c>
       <c r="L9" s="2" t="str">
-        <f>B9</f>
+        <f>C9&amp;"_container"</f>
         <v>develop_config_container</v>
       </c>
     </row>

--- a/Assets/Game/luban/config/tables.xlsx
+++ b/Assets/Game/luban/config/tables.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="14250" windowHeight="7545"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -41,6 +41,9 @@
     <t>read_schema_from_file</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
     <t>从excel读取定义</t>
   </si>
   <si>
+    <t>基础名字</t>
+  </si>
+  <si>
     <t>备注：表名称</t>
   </si>
   <si>
@@ -113,37 +119,37 @@
     <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
   </si>
   <si>
-    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>surname_config</t>
-  </si>
-  <si>
-    <t>general/surname.xlsx</t>
-  </si>
-  <si>
-    <t>name_config</t>
-  </si>
-  <si>
-    <t>general/name.xlsx</t>
-  </si>
-  <si>
-    <t>red_dot_config</t>
-  </si>
-  <si>
-    <t>general/red_dot.xlsx</t>
-  </si>
-  <si>
-    <t>item_config</t>
-  </si>
-  <si>
-    <t>general/item.xlsx</t>
-  </si>
-  <si>
-    <t>develop_config</t>
-  </si>
-  <si>
-    <t>general/develop.xlsx</t>
+    <t>surname</t>
+  </si>
+  <si>
+    <t>姓氏</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>red_dot</t>
+  </si>
+  <si>
+    <t>红点</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>物品</t>
+  </si>
+  <si>
+    <t>develop</t>
+  </si>
+  <si>
+    <t>养成</t>
+  </si>
+  <si>
+    <t>rename_cost</t>
+  </si>
+  <si>
+    <t>改名消耗</t>
   </si>
 </sst>
 </file>
@@ -1135,25 +1141,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="42.7142857142857" style="2" customWidth="1"/>
     <col min="3" max="3" width="38.7142857142857" style="2" customWidth="1"/>
-    <col min="4" max="4" width="61.8571428571429" style="2" customWidth="1"/>
-    <col min="5" max="5" width="54.4285714285714" style="2" customWidth="1"/>
-    <col min="6" max="6" width="49" style="2" customWidth="1"/>
-    <col min="7" max="7" width="69.4285714285714" style="2" customWidth="1"/>
-    <col min="8" max="8" width="51.5714285714286" style="2" customWidth="1"/>
-    <col min="9" max="9" width="61" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.8571428571429" style="2" customWidth="1"/>
-    <col min="12" max="12" width="35.1428571428571" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="4" max="5" width="61.8571428571429" style="2" customWidth="1"/>
+    <col min="6" max="6" width="54.4285714285714" style="2" customWidth="1"/>
+    <col min="7" max="7" width="49" style="2" customWidth="1"/>
+    <col min="8" max="8" width="69.4285714285714" style="2" customWidth="1"/>
+    <col min="9" max="9" width="51.5714285714286" style="2" customWidth="1"/>
+    <col min="10" max="10" width="61" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.8571428571429" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.1428571428571" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,170 +1196,257 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+    <row r="2" s="1" customFormat="1" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:12">
+    <row r="3" s="1" customFormat="1" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="L4" s="2" t="str">
+    <row r="4" spans="1:13">
+      <c r="M4" s="2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(B4,"_",""),".","")</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="B5" s="2" t="str">
-        <f>"container."&amp;L5</f>
-        <v>container.surname_config_container</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
+        <f>IF(M5&lt;&gt;"","game."&amp;M5,"")</f>
+        <v>game.surname_config_container</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f t="shared" ref="C5:C11" si="0">IF(E5&lt;&gt;"",E5&amp;"_config","")</f>
+        <v>surname_config</v>
       </c>
       <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="2" t="str">
-        <f>C5&amp;"_container"</f>
+      <c r="G5" s="2" t="str">
+        <f>IF(E5&lt;&gt;"","general/"&amp;E5&amp;".xlsx","")</f>
+        <v>general/surname.xlsx</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="2" t="str">
+        <f>IF(C5&lt;&gt;"",C5&amp;"_container","")</f>
         <v>surname_config_container</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="B6" s="2" t="str">
-        <f>"container."&amp;L6</f>
-        <v>container.name_config_container</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>31</v>
+        <f t="shared" ref="B6:B11" si="1">IF(M6&lt;&gt;"","game."&amp;M6,"")</f>
+        <v>game.name_config_container</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>name_config</v>
       </c>
       <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <f t="shared" ref="G6:G11" si="2">IF(E6&lt;&gt;"","general/"&amp;E6&amp;".xlsx","")</f>
+        <v>general/name.xlsx</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="2" t="str">
-        <f>C6&amp;"_container"</f>
+      <c r="M6" s="2" t="str">
+        <f t="shared" ref="M6:M11" si="3">IF(C6&lt;&gt;"",C6&amp;"_container","")</f>
         <v>name_config_container</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="B7" s="2" t="str">
-        <f>"container."&amp;L7</f>
-        <v>container.red_dot_config_container</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
+        <f t="shared" si="1"/>
+        <v>game.red_dot_config_container</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>red_dot_config</v>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>general/red_dot.xlsx</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="2" t="str">
-        <f>C7&amp;"_container"</f>
+      <c r="M7" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>red_dot_config_container</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="B8" s="2" t="str">
-        <f>"container."&amp;L8</f>
-        <v>container.item_config_container</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
+        <f t="shared" si="1"/>
+        <v>game.item_config_container</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>item_config</v>
       </c>
       <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>general/item.xlsx</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="2" t="str">
-        <f>C8&amp;"_container"</f>
+      <c r="M8" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>item_config_container</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="B9" s="2" t="str">
-        <f>"container."&amp;L9</f>
-        <v>container.develop_config_container</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>37</v>
+        <f t="shared" si="1"/>
+        <v>game.develop_config_container</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>develop_config</v>
       </c>
       <c r="D9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>general/develop.xlsx</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L9" s="2" t="str">
-        <f>C9&amp;"_container"</f>
+      <c r="M9" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>develop_config_container</v>
       </c>
     </row>
-    <row r="13" customHeight="1"/>
+    <row r="10" spans="1:13">
+      <c r="B10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M10" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="B11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>game.rename_cost_config_container</v>
+      </c>
+      <c r="C11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>rename_cost_config</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>general/rename_cost.xlsx</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>rename_cost_config_container</v>
+      </c>
+    </row>
     <row r="14" customHeight="1"/>
     <row r="15" customHeight="1"/>
     <row r="16" customHeight="1"/>
@@ -1515,21 +1608,13 @@
     <row r="172" customHeight="1"/>
     <row r="173" customHeight="1"/>
     <row r="174" customHeight="1"/>
+    <row r="175" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="C5">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
+  <conditionalFormatting sqref="C5:C11">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C4 C8 C13:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
+  <conditionalFormatting sqref="C1:C4 C14:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" pageOrder="overThenDown" orientation="portrait"/>

--- a/Assets/Game/luban/config/tables.xlsx
+++ b/Assets/Game/luban/config/tables.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>改名消耗</t>
+  </si>
+  <si>
+    <t>default_item</t>
+  </si>
+  <si>
+    <t>默认物品</t>
   </si>
 </sst>
 </file>
@@ -1407,10 +1413,6 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C10" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
       <c r="G10" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -1445,6 +1447,47 @@
       <c r="M11" s="2" t="str">
         <f t="shared" si="3"/>
         <v>rename_cost_config_container</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="B12" s="2" t="str">
+        <f>IF(M12&lt;&gt;"","game."&amp;M12,"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f>IF(E12&lt;&gt;"","general/"&amp;E12&amp;".xlsx","")</f>
+        <v/>
+      </c>
+      <c r="M12" s="2" t="str">
+        <f>IF(C12&lt;&gt;"",C12&amp;"_container","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="B13" s="2" t="str">
+        <f>IF(M13&lt;&gt;"","game."&amp;M13,"")</f>
+        <v>game.default_item_config_container</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <f>IF(E13&lt;&gt;"",E13&amp;"_config","")</f>
+        <v>default_item_config</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f>IF(E13&lt;&gt;"","general/"&amp;E13&amp;".xlsx","")</f>
+        <v>general/default_item.xlsx</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="2" t="str">
+        <f>IF(C13&lt;&gt;"",C13&amp;"_container","")</f>
+        <v>default_item_config_container</v>
       </c>
     </row>
     <row r="14" customHeight="1"/>
@@ -1610,7 +1653,7 @@
     <row r="174" customHeight="1"/>
     <row r="175" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="C5:C11">
+  <conditionalFormatting sqref="C5:C13">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C4 C14:C1048576">

--- a/Assets/Game/luban/config/tables.xlsx
+++ b/Assets/Game/luban/config/tables.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -134,28 +134,34 @@
     <t>红点</t>
   </si>
   <si>
+    <t>rename_cost</t>
+  </si>
+  <si>
+    <t>改名消耗</t>
+  </si>
+  <si>
     <t>item</t>
   </si>
   <si>
     <t>物品</t>
   </si>
   <si>
+    <t>default_item</t>
+  </si>
+  <si>
+    <t>默认物品</t>
+  </si>
+  <si>
     <t>develop</t>
   </si>
   <si>
     <t>养成</t>
   </si>
   <si>
-    <t>rename_cost</t>
-  </si>
-  <si>
-    <t>改名消耗</t>
-  </si>
-  <si>
-    <t>default_item</t>
-  </si>
-  <si>
-    <t>默认物品</t>
+    <t>develop_level</t>
+  </si>
+  <si>
+    <t>养成升级</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1285,7 @@
         <v>game.surname_config_container</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f t="shared" ref="C5:C11" si="0">IF(E5&lt;&gt;"",E5&amp;"_config","")</f>
+        <f>IF(E5&lt;&gt;"",E5&amp;"_config","")</f>
         <v>surname_config</v>
       </c>
       <c r="D5" s="2" t="b">
@@ -1302,11 +1308,11 @@
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="2" t="str">
-        <f t="shared" ref="B6:B11" si="1">IF(M6&lt;&gt;"","game."&amp;M6,"")</f>
+        <f>IF(M6&lt;&gt;"","game."&amp;M6,"")</f>
         <v>game.name_config_container</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E6&lt;&gt;"",E6&amp;"_config","")</f>
         <v>name_config</v>
       </c>
       <c r="D6" s="2" t="b">
@@ -1316,24 +1322,24 @@
         <v>4</v>
       </c>
       <c r="G6" s="2" t="str">
-        <f t="shared" ref="G6:G11" si="2">IF(E6&lt;&gt;"","general/"&amp;E6&amp;".xlsx","")</f>
+        <f>IF(E6&lt;&gt;"","general/"&amp;E6&amp;".xlsx","")</f>
         <v>general/name.xlsx</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M6" s="2" t="str">
-        <f t="shared" ref="M6:M11" si="3">IF(C6&lt;&gt;"",C6&amp;"_container","")</f>
+        <f>IF(C6&lt;&gt;"",C6&amp;"_container","")</f>
         <v>name_config_container</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="B7" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(M7&lt;&gt;"","game."&amp;M7,"")</f>
         <v>game.red_dot_config_container</v>
       </c>
       <c r="C7" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E7&lt;&gt;"",E7&amp;"_config","")</f>
         <v>red_dot_config</v>
       </c>
       <c r="D7" s="2" t="b">
@@ -1343,155 +1349,153 @@
         <v>33</v>
       </c>
       <c r="G7" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(E7&lt;&gt;"","general/"&amp;E7&amp;".xlsx","")</f>
         <v>general/red_dot.xlsx</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M7" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(C7&lt;&gt;"",C7&amp;"_container","")</f>
         <v>red_dot_config_container</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>game.item_config_container</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>item_config</v>
-      </c>
-      <c r="D8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>general/item.xlsx</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>item_config_container</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="B9" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>game.develop_config_container</v>
+        <f>IF(M9&lt;&gt;"","game."&amp;M9,"")</f>
+        <v>game.rename_cost_config_container</v>
       </c>
       <c r="C9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>develop_config</v>
+        <f>IF(E9&lt;&gt;"",E9&amp;"_config","")</f>
+        <v>rename_cost_config</v>
       </c>
       <c r="D9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>general/develop.xlsx</v>
+        <f>IF(E9&lt;&gt;"","general/"&amp;E9&amp;".xlsx","")</f>
+        <v>general/rename_cost.xlsx</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M9" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>develop_config_container</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G10" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="M10" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f>IF(C9&lt;&gt;"",C9&amp;"_container","")</f>
+        <v>rename_cost_config_container</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="B11" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>game.rename_cost_config_container</v>
+        <f>IF(M11&lt;&gt;"","game."&amp;M11,"")</f>
+        <v>game.item_config_container</v>
       </c>
       <c r="C11" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>rename_cost_config</v>
+        <f>IF(E11&lt;&gt;"",E11&amp;"_config","")</f>
+        <v>item_config</v>
       </c>
       <c r="D11" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G11" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>general/rename_cost.xlsx</v>
+        <f>IF(E11&lt;&gt;"","general/"&amp;E11&amp;".xlsx","")</f>
+        <v>general/item.xlsx</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M11" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>rename_cost_config_container</v>
+        <f>IF(C11&lt;&gt;"",C11&amp;"_container","")</f>
+        <v>item_config_container</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="B12" s="2" t="str">
         <f>IF(M12&lt;&gt;"","game."&amp;M12,"")</f>
-        <v/>
+        <v>game.default_item_config_container</v>
+      </c>
+      <c r="C12" s="2" t="str">
+        <f>IF(E12&lt;&gt;"",E12&amp;"_config","")</f>
+        <v>default_item_config</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="G12" s="2" t="str">
         <f>IF(E12&lt;&gt;"","general/"&amp;E12&amp;".xlsx","")</f>
-        <v/>
+        <v>general/default_item.xlsx</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="M12" s="2" t="str">
         <f>IF(C12&lt;&gt;"",C12&amp;"_container","")</f>
-        <v/>
+        <v>default_item_config_container</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="2" t="str">
-        <f>IF(M13&lt;&gt;"","game."&amp;M13,"")</f>
-        <v>game.default_item_config_container</v>
-      </c>
-      <c r="C13" s="2" t="str">
-        <f>IF(E13&lt;&gt;"",E13&amp;"_config","")</f>
-        <v>default_item_config</v>
-      </c>
-      <c r="D13" s="2" t="b">
+    <row r="13" customHeight="1"/>
+    <row r="14" spans="1:13">
+      <c r="B14" s="2" t="str">
+        <f>IF(M14&lt;&gt;"","game."&amp;M14,"")</f>
+        <v>game.develop_config_container</v>
+      </c>
+      <c r="C14" s="2" t="str">
+        <f>IF(E14&lt;&gt;"",E14&amp;"_config","")</f>
+        <v>develop_config</v>
+      </c>
+      <c r="D14" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="2" t="str">
-        <f>IF(E13&lt;&gt;"","general/"&amp;E13&amp;".xlsx","")</f>
-        <v>general/default_item.xlsx</v>
-      </c>
-      <c r="K13" s="2" t="s">
+      <c r="G14" s="2" t="str">
+        <f>IF(E14&lt;&gt;"","general/"&amp;E14&amp;".xlsx","")</f>
+        <v>general/develop.xlsx</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M13" s="2" t="str">
-        <f>IF(C13&lt;&gt;"",C13&amp;"_container","")</f>
-        <v>default_item_config_container</v>
+      <c r="M14" s="2" t="str">
+        <f>IF(C14&lt;&gt;"",C14&amp;"_container","")</f>
+        <v>develop_config_container</v>
       </c>
     </row>
-    <row r="14" customHeight="1"/>
-    <row r="15" customHeight="1"/>
+    <row r="15" customHeight="1" spans="1:13">
+      <c r="B15" s="2" t="str">
+        <f>IF(M15&lt;&gt;"","game."&amp;M15,"")</f>
+        <v>game.develop_level_config_container</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f>IF(E15&lt;&gt;"",E15&amp;"_config","")</f>
+        <v>develop_level_config</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="2" t="str">
+        <f>IF(E15&lt;&gt;"","general/"&amp;E15&amp;".xlsx","")</f>
+        <v>general/develop_level.xlsx</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M15" s="2" t="str">
+        <f>IF(C15&lt;&gt;"",C15&amp;"_container","")</f>
+        <v>develop_level_config_container</v>
+      </c>
+    </row>
     <row r="16" customHeight="1"/>
     <row r="17" customHeight="1"/>
     <row r="18" customHeight="1"/>
@@ -1653,11 +1657,11 @@
     <row r="174" customHeight="1"/>
     <row r="175" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="C5:C13">
+  <conditionalFormatting sqref="C1:C4 C13 C16:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C7 C9:C12 C14:C15">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C4 C14:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" pageOrder="overThenDown" orientation="portrait"/>

--- a/Assets/Game/luban/config/tables.xlsx
+++ b/Assets/Game/luban/config/tables.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -162,6 +162,18 @@
   </si>
   <si>
     <t>养成升级</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t>任务</t>
+  </si>
+  <si>
+    <t>avatar</t>
+  </si>
+  <si>
+    <t>头像</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1432,7 @@
         <v>game.default_item_config_container</v>
       </c>
       <c r="C12" s="2" t="str">
-        <f>IF(E12&lt;&gt;"",E12&amp;"_config","")</f>
+        <f t="shared" ref="C12:C17" si="0">IF(E12&lt;&gt;"",E12&amp;"_config","")</f>
         <v>default_item_config</v>
       </c>
       <c r="D12" s="2" t="b">
@@ -1448,7 +1460,7 @@
         <v>game.develop_config_container</v>
       </c>
       <c r="C14" s="2" t="str">
-        <f>IF(E14&lt;&gt;"",E14&amp;"_config","")</f>
+        <f t="shared" si="0"/>
         <v>develop_config</v>
       </c>
       <c r="D14" s="2" t="b">
@@ -1475,7 +1487,7 @@
         <v>game.develop_level_config_container</v>
       </c>
       <c r="C15" s="2" t="str">
-        <f>IF(E15&lt;&gt;"",E15&amp;"_config","")</f>
+        <f t="shared" si="0"/>
         <v>develop_level_config</v>
       </c>
       <c r="D15" s="2" t="b">
@@ -1496,10 +1508,92 @@
         <v>develop_level_config_container</v>
       </c>
     </row>
-    <row r="16" customHeight="1"/>
-    <row r="17" customHeight="1"/>
-    <row r="18" customHeight="1"/>
-    <row r="19" customHeight="1"/>
+    <row r="16" customHeight="1" spans="1:13">
+      <c r="B16" s="2" t="str">
+        <f>IF(M16&lt;&gt;"","game."&amp;M16,"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str">
+        <f>IF(E16&lt;&gt;"","general/"&amp;E16&amp;".xlsx","")</f>
+        <v/>
+      </c>
+      <c r="M16" s="2" t="str">
+        <f>IF(C16&lt;&gt;"",C16&amp;"_container","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:13">
+      <c r="B17" s="2" t="str">
+        <f>IF(M17&lt;&gt;"","game."&amp;M17,"")</f>
+        <v>game.task_config_container</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>task_config</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="2" t="str">
+        <f>IF(E17&lt;&gt;"","general/"&amp;E17&amp;".xlsx","")</f>
+        <v>general/task.xlsx</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M17" s="2" t="str">
+        <f>IF(C17&lt;&gt;"",C17&amp;"_container","")</f>
+        <v>task_config_container</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:13">
+      <c r="B18" s="2" t="str">
+        <f>IF(M18&lt;&gt;"","game."&amp;M18,"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str">
+        <f>IF(E18&lt;&gt;"","general/"&amp;E18&amp;".xlsx","")</f>
+        <v/>
+      </c>
+      <c r="M18" s="2" t="str">
+        <f>IF(C18&lt;&gt;"",C18&amp;"_container","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:13">
+      <c r="B19" s="2" t="str">
+        <f>IF(M19&lt;&gt;"","game."&amp;M19,"")</f>
+        <v>game.avatar_config_container</v>
+      </c>
+      <c r="C19" s="2" t="str">
+        <f>IF(E19&lt;&gt;"",E19&amp;"_config","")</f>
+        <v>avatar_config</v>
+      </c>
+      <c r="D19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="2" t="str">
+        <f>IF(E19&lt;&gt;"","general/"&amp;E19&amp;".xlsx","")</f>
+        <v>general/avatar.xlsx</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M19" s="2" t="str">
+        <f>IF(C19&lt;&gt;"",C19&amp;"_container","")</f>
+        <v>avatar_config_container</v>
+      </c>
+    </row>
     <row r="20" customHeight="1"/>
     <row r="21" customHeight="1"/>
     <row r="22" customHeight="1"/>
@@ -1657,11 +1751,14 @@
     <row r="174" customHeight="1"/>
     <row r="175" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="C1:C4 C13 C16:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C7 C9:C12 C14:C15">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="C1:C4 C13 C18 C20:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C7 C9:C12 C14:C17">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" pageOrder="overThenDown" orientation="portrait"/>

--- a/Assets/Game/luban/config/tables.xlsx
+++ b/Assets/Game/luban/config/tables.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -152,6 +152,18 @@
     <t>默认物品</t>
   </si>
   <si>
+    <t>avatar</t>
+  </si>
+  <si>
+    <t>头像</t>
+  </si>
+  <si>
+    <t>hero</t>
+  </si>
+  <si>
+    <t>英雄</t>
+  </si>
+  <si>
     <t>develop</t>
   </si>
   <si>
@@ -168,12 +180,6 @@
   </si>
   <si>
     <t>任务</t>
-  </si>
-  <si>
-    <t>avatar</t>
-  </si>
-  <si>
-    <t>头像</t>
   </si>
 </sst>
 </file>
@@ -1165,7 +1171,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1432,7 +1438,7 @@
         <v>game.default_item_config_container</v>
       </c>
       <c r="C12" s="2" t="str">
-        <f t="shared" ref="C12:C17" si="0">IF(E12&lt;&gt;"",E12&amp;"_config","")</f>
+        <f>IF(E12&lt;&gt;"",E12&amp;"_config","")</f>
         <v>default_item_config</v>
       </c>
       <c r="D12" s="2" t="b">
@@ -1453,104 +1459,113 @@
         <v>default_item_config_container</v>
       </c>
     </row>
-    <row r="13" customHeight="1"/>
-    <row r="14" spans="1:13">
+    <row r="13" customHeight="1" spans="1:13">
+      <c r="B13" s="2" t="str">
+        <f>IF(M13&lt;&gt;"","game."&amp;M13,"")</f>
+        <v>game.avatar_config_container</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <f>IF(E13&lt;&gt;"",E13&amp;"_config","")</f>
+        <v>avatar_config</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f>IF(E13&lt;&gt;"","general/"&amp;E13&amp;".xlsx","")</f>
+        <v>general/avatar.xlsx</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="2" t="str">
+        <f>IF(C13&lt;&gt;"",C13&amp;"_container","")</f>
+        <v>avatar_config_container</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:13">
       <c r="B14" s="2" t="str">
         <f>IF(M14&lt;&gt;"","game."&amp;M14,"")</f>
-        <v>game.develop_config_container</v>
+        <v>game.hero_config_container</v>
       </c>
       <c r="C14" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>develop_config</v>
+        <f>IF(E14&lt;&gt;"",E14&amp;"_config","")</f>
+        <v>hero_config</v>
       </c>
       <c r="D14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G14" s="2" t="str">
         <f>IF(E14&lt;&gt;"","general/"&amp;E14&amp;".xlsx","")</f>
-        <v>general/develop.xlsx</v>
+        <v>general/hero.xlsx</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M14" s="2" t="str">
         <f>IF(C14&lt;&gt;"",C14&amp;"_container","")</f>
-        <v>develop_config_container</v>
+        <v>hero_config_container</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:13">
-      <c r="B15" s="2" t="str">
-        <f>IF(M15&lt;&gt;"","game."&amp;M15,"")</f>
-        <v>game.develop_level_config_container</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>develop_level_config</v>
-      </c>
-      <c r="D15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="2" t="str">
-        <f>IF(E15&lt;&gt;"","general/"&amp;E15&amp;".xlsx","")</f>
-        <v>general/develop_level.xlsx</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M15" s="2" t="str">
-        <f>IF(C15&lt;&gt;"",C15&amp;"_container","")</f>
-        <v>develop_level_config_container</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:13">
+    <row r="15" customHeight="1"/>
+    <row r="16" spans="1:13">
       <c r="B16" s="2" t="str">
         <f>IF(M16&lt;&gt;"","game."&amp;M16,"")</f>
-        <v/>
+        <v>game.develop_config_container</v>
       </c>
       <c r="C16" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(E16&lt;&gt;"",E16&amp;"_config","")</f>
+        <v>develop_config</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="G16" s="2" t="str">
         <f>IF(E16&lt;&gt;"","general/"&amp;E16&amp;".xlsx","")</f>
-        <v/>
+        <v>general/develop.xlsx</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="M16" s="2" t="str">
         <f>IF(C16&lt;&gt;"",C16&amp;"_container","")</f>
-        <v/>
+        <v>develop_config_container</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:13">
       <c r="B17" s="2" t="str">
         <f>IF(M17&lt;&gt;"","game."&amp;M17,"")</f>
-        <v>game.task_config_container</v>
+        <v>game.develop_level_config_container</v>
       </c>
       <c r="C17" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>task_config</v>
+        <f>IF(E17&lt;&gt;"",E17&amp;"_config","")</f>
+        <v>develop_level_config</v>
       </c>
       <c r="D17" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G17" s="2" t="str">
         <f>IF(E17&lt;&gt;"","general/"&amp;E17&amp;".xlsx","")</f>
-        <v>general/task.xlsx</v>
+        <v>general/develop_level.xlsx</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M17" s="2" t="str">
         <f>IF(C17&lt;&gt;"",C17&amp;"_container","")</f>
-        <v>task_config_container</v>
+        <v>develop_level_config_container</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:13">
@@ -1558,6 +1573,10 @@
         <f>IF(M18&lt;&gt;"","game."&amp;M18,"")</f>
         <v/>
       </c>
+      <c r="C18" s="2" t="str">
+        <f>IF(E18&lt;&gt;"",E18&amp;"_config","")</f>
+        <v/>
+      </c>
       <c r="G18" s="2" t="str">
         <f>IF(E18&lt;&gt;"","general/"&amp;E18&amp;".xlsx","")</f>
         <v/>
@@ -1570,31 +1589,44 @@
     <row r="19" customHeight="1" spans="2:13">
       <c r="B19" s="2" t="str">
         <f>IF(M19&lt;&gt;"","game."&amp;M19,"")</f>
-        <v>game.avatar_config_container</v>
+        <v>game.task_config_container</v>
       </c>
       <c r="C19" s="2" t="str">
         <f>IF(E19&lt;&gt;"",E19&amp;"_config","")</f>
-        <v>avatar_config</v>
+        <v>task_config</v>
       </c>
       <c r="D19" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2" t="str">
         <f>IF(E19&lt;&gt;"","general/"&amp;E19&amp;".xlsx","")</f>
-        <v>general/avatar.xlsx</v>
+        <v>general/task.xlsx</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M19" s="2" t="str">
         <f>IF(C19&lt;&gt;"",C19&amp;"_container","")</f>
-        <v>avatar_config_container</v>
+        <v>task_config_container</v>
       </c>
     </row>
-    <row r="20" customHeight="1"/>
+    <row r="20" customHeight="1" spans="2:13">
+      <c r="B20" s="2" t="str">
+        <f>IF(M20&lt;&gt;"","game."&amp;M20,"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str">
+        <f>IF(E20&lt;&gt;"","general/"&amp;E20&amp;".xlsx","")</f>
+        <v/>
+      </c>
+      <c r="M20" s="2" t="str">
+        <f>IF(C20&lt;&gt;"",C20&amp;"_container","")</f>
+        <v/>
+      </c>
+    </row>
     <row r="21" customHeight="1"/>
     <row r="22" customHeight="1"/>
     <row r="23" customHeight="1"/>
@@ -1749,15 +1781,14 @@
     <row r="172" customHeight="1"/>
     <row r="173" customHeight="1"/>
     <row r="174" customHeight="1"/>
-    <row r="175" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="C19">
+  <conditionalFormatting sqref="C13:C14">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C4 C13 C18 C20:C1048576">
+  <conditionalFormatting sqref="C1:C4 C15 C20:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C7 C9:C12 C14:C17">
+  <conditionalFormatting sqref="C5:C7 C9:C12 C16:C19">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Game/luban/config/tables.xlsx
+++ b/Assets/Game/luban/config/tables.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -156,6 +156,12 @@
   </si>
   <si>
     <t>头像</t>
+  </si>
+  <si>
+    <t>frame</t>
+  </si>
+  <si>
+    <t>头像框</t>
   </si>
   <si>
     <t>hero</t>
@@ -1171,7 +1177,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M174"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1489,11 +1495,11 @@
     <row r="14" customHeight="1" spans="1:13">
       <c r="B14" s="2" t="str">
         <f>IF(M14&lt;&gt;"","game."&amp;M14,"")</f>
-        <v>game.hero_config_container</v>
+        <v>game.frame_config_container</v>
       </c>
       <c r="C14" s="2" t="str">
         <f>IF(E14&lt;&gt;"",E14&amp;"_config","")</f>
-        <v>hero_config</v>
+        <v>frame_config</v>
       </c>
       <c r="D14" s="2" t="b">
         <v>1</v>
@@ -1503,52 +1509,52 @@
       </c>
       <c r="G14" s="2" t="str">
         <f>IF(E14&lt;&gt;"","general/"&amp;E14&amp;".xlsx","")</f>
-        <v>general/hero.xlsx</v>
+        <v>general/frame.xlsx</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="M14" s="2" t="str">
         <f>IF(C14&lt;&gt;"",C14&amp;"_container","")</f>
+        <v>frame_config_container</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:13">
+      <c r="B15" s="2" t="str">
+        <f>IF(M15&lt;&gt;"","game."&amp;M15,"")</f>
+        <v>game.hero_config_container</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f>IF(E15&lt;&gt;"",E15&amp;"_config","")</f>
+        <v>hero_config</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="2" t="str">
+        <f>IF(E15&lt;&gt;"","general/"&amp;E15&amp;".xlsx","")</f>
+        <v>general/hero.xlsx</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="2" t="str">
+        <f>IF(C15&lt;&gt;"",C15&amp;"_container","")</f>
         <v>hero_config_container</v>
       </c>
     </row>
-    <row r="15" customHeight="1"/>
-    <row r="16" spans="1:13">
-      <c r="B16" s="2" t="str">
-        <f>IF(M16&lt;&gt;"","game."&amp;M16,"")</f>
-        <v>game.develop_config_container</v>
-      </c>
-      <c r="C16" s="2" t="str">
-        <f>IF(E16&lt;&gt;"",E16&amp;"_config","")</f>
-        <v>develop_config</v>
-      </c>
-      <c r="D16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="2" t="str">
-        <f>IF(E16&lt;&gt;"","general/"&amp;E16&amp;".xlsx","")</f>
-        <v>general/develop.xlsx</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" s="2" t="str">
-        <f>IF(C16&lt;&gt;"",C16&amp;"_container","")</f>
-        <v>develop_config_container</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="2:13">
+    <row r="16" customHeight="1"/>
+    <row r="17" spans="2:13">
       <c r="B17" s="2" t="str">
         <f>IF(M17&lt;&gt;"","game."&amp;M17,"")</f>
-        <v>game.develop_level_config_container</v>
+        <v>game.develop_config_container</v>
       </c>
       <c r="C17" s="2" t="str">
         <f>IF(E17&lt;&gt;"",E17&amp;"_config","")</f>
-        <v>develop_level_config</v>
+        <v>develop_config</v>
       </c>
       <c r="D17" s="2" t="b">
         <v>1</v>
@@ -1558,76 +1564,102 @@
       </c>
       <c r="G17" s="2" t="str">
         <f>IF(E17&lt;&gt;"","general/"&amp;E17&amp;".xlsx","")</f>
-        <v>general/develop_level.xlsx</v>
+        <v>general/develop.xlsx</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>48</v>
       </c>
       <c r="M17" s="2" t="str">
         <f>IF(C17&lt;&gt;"",C17&amp;"_container","")</f>
-        <v>develop_level_config_container</v>
+        <v>develop_config_container</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:13">
       <c r="B18" s="2" t="str">
         <f>IF(M18&lt;&gt;"","game."&amp;M18,"")</f>
-        <v/>
+        <v>game.develop_level_config_container</v>
       </c>
       <c r="C18" s="2" t="str">
         <f>IF(E18&lt;&gt;"",E18&amp;"_config","")</f>
-        <v/>
+        <v>develop_level_config</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="G18" s="2" t="str">
         <f>IF(E18&lt;&gt;"","general/"&amp;E18&amp;".xlsx","")</f>
-        <v/>
+        <v>general/develop_level.xlsx</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="M18" s="2" t="str">
         <f>IF(C18&lt;&gt;"",C18&amp;"_container","")</f>
-        <v/>
+        <v>develop_level_config_container</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:13">
       <c r="B19" s="2" t="str">
         <f>IF(M19&lt;&gt;"","game."&amp;M19,"")</f>
-        <v>game.task_config_container</v>
+        <v/>
       </c>
       <c r="C19" s="2" t="str">
         <f>IF(E19&lt;&gt;"",E19&amp;"_config","")</f>
-        <v>task_config</v>
-      </c>
-      <c r="D19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>49</v>
+        <v/>
       </c>
       <c r="G19" s="2" t="str">
         <f>IF(E19&lt;&gt;"","general/"&amp;E19&amp;".xlsx","")</f>
-        <v>general/task.xlsx</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>50</v>
+        <v/>
       </c>
       <c r="M19" s="2" t="str">
         <f>IF(C19&lt;&gt;"",C19&amp;"_container","")</f>
-        <v>task_config_container</v>
+        <v/>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:13">
       <c r="B20" s="2" t="str">
         <f>IF(M20&lt;&gt;"","game."&amp;M20,"")</f>
-        <v/>
+        <v>game.task_config_container</v>
+      </c>
+      <c r="C20" s="2" t="str">
+        <f>IF(E20&lt;&gt;"",E20&amp;"_config","")</f>
+        <v>task_config</v>
+      </c>
+      <c r="D20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="G20" s="2" t="str">
         <f>IF(E20&lt;&gt;"","general/"&amp;E20&amp;".xlsx","")</f>
-        <v/>
+        <v>general/task.xlsx</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="M20" s="2" t="str">
         <f>IF(C20&lt;&gt;"",C20&amp;"_container","")</f>
+        <v>task_config_container</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:13">
+      <c r="B21" s="2" t="str">
+        <f>IF(M21&lt;&gt;"","game."&amp;M21,"")</f>
         <v/>
       </c>
+      <c r="G21" s="2" t="str">
+        <f>IF(E21&lt;&gt;"","general/"&amp;E21&amp;".xlsx","")</f>
+        <v/>
+      </c>
+      <c r="M21" s="2" t="str">
+        <f>IF(C21&lt;&gt;"",C21&amp;"_container","")</f>
+        <v/>
+      </c>
     </row>
-    <row r="21" customHeight="1"/>
     <row r="22" customHeight="1"/>
     <row r="23" customHeight="1"/>
     <row r="24" customHeight="1"/>
@@ -1781,14 +1813,15 @@
     <row r="172" customHeight="1"/>
     <row r="173" customHeight="1"/>
     <row r="174" customHeight="1"/>
+    <row r="175" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="C13:C14">
+  <conditionalFormatting sqref="C13:C15">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C4 C15 C20:C1048576">
+  <conditionalFormatting sqref="C1:C4 C16 C21:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C7 C9:C12 C16:C19">
+  <conditionalFormatting sqref="C5:C7 C9:C12 C17:C20">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Game/luban/config/tables.xlsx
+++ b/Assets/Game/luban/config/tables.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>头像框</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>称号</t>
   </si>
   <si>
     <t>hero</t>
@@ -1177,7 +1183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1522,11 +1528,11 @@
     <row r="15" customHeight="1" spans="1:13">
       <c r="B15" s="2" t="str">
         <f>IF(M15&lt;&gt;"","game."&amp;M15,"")</f>
-        <v>game.hero_config_container</v>
+        <v>game.title_config_container</v>
       </c>
       <c r="C15" s="2" t="str">
         <f>IF(E15&lt;&gt;"",E15&amp;"_config","")</f>
-        <v>hero_config</v>
+        <v>title_config</v>
       </c>
       <c r="D15" s="2" t="b">
         <v>1</v>
@@ -1536,52 +1542,52 @@
       </c>
       <c r="G15" s="2" t="str">
         <f>IF(E15&lt;&gt;"","general/"&amp;E15&amp;".xlsx","")</f>
-        <v>general/hero.xlsx</v>
+        <v>general/title.xlsx</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M15" s="2" t="str">
         <f>IF(C15&lt;&gt;"",C15&amp;"_container","")</f>
+        <v>title_config_container</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:13">
+      <c r="B16" s="2" t="str">
+        <f>IF(M16&lt;&gt;"","game."&amp;M16,"")</f>
+        <v>game.hero_config_container</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>IF(E16&lt;&gt;"",E16&amp;"_config","")</f>
+        <v>hero_config</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="2" t="str">
+        <f>IF(E16&lt;&gt;"","general/"&amp;E16&amp;".xlsx","")</f>
+        <v>general/hero.xlsx</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" s="2" t="str">
+        <f>IF(C16&lt;&gt;"",C16&amp;"_container","")</f>
         <v>hero_config_container</v>
       </c>
     </row>
-    <row r="16" customHeight="1"/>
-    <row r="17" spans="2:13">
-      <c r="B17" s="2" t="str">
-        <f>IF(M17&lt;&gt;"","game."&amp;M17,"")</f>
-        <v>game.develop_config_container</v>
-      </c>
-      <c r="C17" s="2" t="str">
-        <f>IF(E17&lt;&gt;"",E17&amp;"_config","")</f>
-        <v>develop_config</v>
-      </c>
-      <c r="D17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="2" t="str">
-        <f>IF(E17&lt;&gt;"","general/"&amp;E17&amp;".xlsx","")</f>
-        <v>general/develop.xlsx</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M17" s="2" t="str">
-        <f>IF(C17&lt;&gt;"",C17&amp;"_container","")</f>
-        <v>develop_config_container</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="2:13">
+    <row r="17" customHeight="1"/>
+    <row r="18" spans="2:13">
       <c r="B18" s="2" t="str">
         <f>IF(M18&lt;&gt;"","game."&amp;M18,"")</f>
-        <v>game.develop_level_config_container</v>
+        <v>game.develop_config_container</v>
       </c>
       <c r="C18" s="2" t="str">
         <f>IF(E18&lt;&gt;"",E18&amp;"_config","")</f>
-        <v>develop_level_config</v>
+        <v>develop_config</v>
       </c>
       <c r="D18" s="2" t="b">
         <v>1</v>
@@ -1591,76 +1597,102 @@
       </c>
       <c r="G18" s="2" t="str">
         <f>IF(E18&lt;&gt;"","general/"&amp;E18&amp;".xlsx","")</f>
-        <v>general/develop_level.xlsx</v>
+        <v>general/develop.xlsx</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M18" s="2" t="str">
         <f>IF(C18&lt;&gt;"",C18&amp;"_container","")</f>
-        <v>develop_level_config_container</v>
+        <v>develop_config_container</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:13">
       <c r="B19" s="2" t="str">
         <f>IF(M19&lt;&gt;"","game."&amp;M19,"")</f>
-        <v/>
+        <v>game.develop_level_config_container</v>
       </c>
       <c r="C19" s="2" t="str">
         <f>IF(E19&lt;&gt;"",E19&amp;"_config","")</f>
-        <v/>
+        <v>develop_level_config</v>
+      </c>
+      <c r="D19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="G19" s="2" t="str">
         <f>IF(E19&lt;&gt;"","general/"&amp;E19&amp;".xlsx","")</f>
-        <v/>
+        <v>general/develop_level.xlsx</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="M19" s="2" t="str">
         <f>IF(C19&lt;&gt;"",C19&amp;"_container","")</f>
-        <v/>
+        <v>develop_level_config_container</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:13">
       <c r="B20" s="2" t="str">
         <f>IF(M20&lt;&gt;"","game."&amp;M20,"")</f>
-        <v>game.task_config_container</v>
+        <v/>
       </c>
       <c r="C20" s="2" t="str">
         <f>IF(E20&lt;&gt;"",E20&amp;"_config","")</f>
-        <v>task_config</v>
-      </c>
-      <c r="D20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>51</v>
+        <v/>
       </c>
       <c r="G20" s="2" t="str">
         <f>IF(E20&lt;&gt;"","general/"&amp;E20&amp;".xlsx","")</f>
-        <v>general/task.xlsx</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>52</v>
+        <v/>
       </c>
       <c r="M20" s="2" t="str">
         <f>IF(C20&lt;&gt;"",C20&amp;"_container","")</f>
-        <v>task_config_container</v>
+        <v/>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:13">
       <c r="B21" s="2" t="str">
         <f>IF(M21&lt;&gt;"","game."&amp;M21,"")</f>
-        <v/>
+        <v>game.task_config_container</v>
+      </c>
+      <c r="C21" s="2" t="str">
+        <f>IF(E21&lt;&gt;"",E21&amp;"_config","")</f>
+        <v>task_config</v>
+      </c>
+      <c r="D21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G21" s="2" t="str">
         <f>IF(E21&lt;&gt;"","general/"&amp;E21&amp;".xlsx","")</f>
-        <v/>
+        <v>general/task.xlsx</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="M21" s="2" t="str">
         <f>IF(C21&lt;&gt;"",C21&amp;"_container","")</f>
+        <v>task_config_container</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="2:13">
+      <c r="B22" s="2" t="str">
+        <f>IF(M22&lt;&gt;"","game."&amp;M22,"")</f>
         <v/>
       </c>
+      <c r="G22" s="2" t="str">
+        <f>IF(E22&lt;&gt;"","general/"&amp;E22&amp;".xlsx","")</f>
+        <v/>
+      </c>
+      <c r="M22" s="2" t="str">
+        <f>IF(C22&lt;&gt;"",C22&amp;"_container","")</f>
+        <v/>
+      </c>
     </row>
-    <row r="22" customHeight="1"/>
     <row r="23" customHeight="1"/>
     <row r="24" customHeight="1"/>
     <row r="25" customHeight="1"/>
@@ -1814,14 +1846,15 @@
     <row r="173" customHeight="1"/>
     <row r="174" customHeight="1"/>
     <row r="175" customHeight="1"/>
+    <row r="176" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="C13:C15">
+  <conditionalFormatting sqref="C13:C16">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C4 C16 C21:C1048576">
+  <conditionalFormatting sqref="C1:C4 C17 C22:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C7 C9:C12 C17:C20">
+  <conditionalFormatting sqref="C5:C7 C9:C12 C18:C21">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
